--- a/요구사항정의서_엑셀양식_v3_1_3.xlsx
+++ b/요구사항정의서_엑셀양식_v3_1_3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DEV\sourcecode\Java-Service-Tree-Framework\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E61999FE-C418-46ED-81A8-E08CEAAC2FF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4237E723-5C69-4C77-9698-CB46FE48B12F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-9795" yWindow="-21600" windowWidth="28950" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9900" yWindow="1350" windowWidth="26895" windowHeight="20790" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="요구사항정의서" sheetId="1" r:id="rId1"/>
@@ -237,32 +237,11 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>멀티에이전트를 지원하기 위하여, 개발용 에이전트먀 ( Role : Reviewer ) 를 구성하기</t>
+    <t>REQ-LANDING-FUNC-02</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>REQ-AIAGENT-DEV-02</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>[개요]
-멀티에이전트 워커 풀에서 ollama 워커를 완전 삭제하고,
-그 자리를 결정론적 검사 + RAG 기반 LLM 판정의 하이브리드 Reviewer Agent 를 구성하려고 한다.
-설계 방향:
-Spring AI 프레임워크를 기반으로
-멀티 에이전트로써 Reviewer Agent 기능을 탑재한다.
-Opensearch 의 벡터 디비를 활용해서, 리뷰를 진행할 수 있는 기능도 추가한다.
-[상세 기능 요구사항]
-PMBOK 을 기준으로 Project Charter 와 SRS 를 작성한다.
-[입력 / 출력]
-[제약 조건 / 비기능 요구사항]
-[검증 기준]
-[작업 대상]
-Dev-Ai-Agent 프로젝트
-[Worker Settings]
-- MainWorker                : claude-main
-- SubWorker                 : codex-critic
-- MainWorker-SubAgent   : N/A</t>
+    <t>랜딩 페이지 국제화 반영</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
@@ -324,11 +303,28 @@
 - common.css 와 기존에 구현된 html에서 사용된 css를 전부 확인하여, 통일성있는 디자인과 색감을 사용할 것.
 [작업 대상]
 Java-Service-Tree-Framework-Frontend-Web 모듈의 arms\html\landing_function에 작업해 줘
-기존 작업은 무시하고 작업 해
 [Worker Settings]
 - MainWoker : claude-main
 - SubWorker : codex-critic
 - MainWoker-SubAgent : frontend-expert</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>[개요]
+A-RMS 는 이미 언어팩(ko,jp,en) 을 제공하고 있다.
+현재 landing_ 으로 시작하는 페이지는 해당 기능이 없다.
+따라서, 기존 구현 내용을 파악하여, landing_ 페이지에 언어팩을 제공하고자 한다.
+설계 방향:
+[상세 기능 요구사항]
+[입력 / 출력]
+[제약 조건 / 비기능 요구사항]
+[검증 기준]
+[작업 대상]
+Java-Service-Tree-Framework-Frontend-Web 모듈의 arms\html\landing_index 에 작업해 줘
+[Worker Settings]
+- MainWorker                : claude-main
+- SubWorker                 : codex-critic
+- MainWorker-SubAgent   : N/A</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
@@ -959,7 +955,7 @@
         <v>61</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>12</v>
@@ -980,9 +976,9 @@
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="337.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="14" t="s">
-        <v>67</v>
+    <row r="3" spans="1:12" ht="310.5" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>63</v>
@@ -992,10 +988,10 @@
       </c>
       <c r="D3" s="14"/>
       <c r="E3" s="15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G3" s="14" t="s">
         <v>65</v>

--- a/요구사항정의서_엑셀양식_v3_1_3.xlsx
+++ b/요구사항정의서_엑셀양식_v3_1_3.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="71">
   <si>
     <t>요구사항 ID</t>
   </si>
@@ -233,20 +233,13 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>[개요]
-backend 의 엔드포인트 목록을 찾아내서, 각각 의 호출되는 메소드들을 분석한다.
+    <t xml:space="preserve">[개요]
+Backend 의 엔드포인트 Rest API 목록을 찾아낸다.
 [상세 기능 요구사항]
-1. 엔드포인트를 전수 식별해 1건 = 1행인 표로 만든다.
-   열 = HTTP · 경로 · 컨트롤러 · 컨트롤러 메서드 · 파일:라인 · 호출 메서드 · Feign
-2. 상속으로 생기는 엔드포인트는 부모를 1회만 기재하고 상속 컨트롤러 목록을 붙인다.
-3. 호출 메서드가 Feign 이면 어느 클라이언트의 어느 메서드인지 적는다.
-   서비스를 거쳐 나가면 그 표시를 남긴다.
-4. 추출하지 못한 행은 비우지 말고 사유를 적는다.
-5. 호출 메서드가 다시 무엇을 부르는지 체인으로 전개한다. 최대 깊이를 명시한다.
-   같은 클래스의 로컬 메서드를 거친 경우 그 경로를 표시한다.
+컨트롤러 별로 나열된 API 목록들을 플랫하게 나열한다.
+ex) controller class name, rest end point, package name, etc …
 [입력 / 출력]
-- 출력 : 엔드포인트 카탈로그 1건 (PDF)
-         표 원본 CSV 1건 (검색·필터용)
+- 출력 : CSV
 [제약 조건 / 비기능 요구사항]
 - 읽기 전용. 코드 수정·실행 금지.
 - 레퍼런스 문서다. 구조 비평·결함 지적·개선 권고는 이 요구사항의 산출물이 아니다.
@@ -254,19 +247,8 @@
 [검증 기준]
 - 자체 선언 엔드포인트가 표에 빠짐없이 있다.
 - 상속 엔드포인트가 1회 기재되고 상속 컨트롤러가 열거돼 있다.
-- Feign 클라이언트가 전수 기재돼 있다.
-- 호출 메서드가 비어 있는 행은 전부 사유가 적혀 있다.
-- 호출 체인이 전개돼 있고, 깊이 상한과 잘린 경로의 처리 방식이 적혀 있다.
 [작업 대상]
 Java-Service-Tree-Framework-Backend-Core
-게이트웨이 경로 규칙 — 프론트가 부르는 외부 경로는 내부 경로와 다르다.
-  /{권한}/{서비스}/**  →  rewrite  →  내부 경로
-  권한   auth-anon → /anonymous/    auth-user → /
-         auth-manager → /manager/   auth-admin → /admin/
-  서비스 api=Backend-Core  ai=AI  yml=Global-Config
-         search=Engine-Fire  hub=Broker-Hub
-  예외   /dwr/** 는 Backend-Core 로 변환 없이 전달. *-api/** 는 스웨거.
-         auth-anon 계열은 쿠키를 떼고(RemoveRequestHeader=Cookie) 넘긴다.
 [Worker Settings]
 - MainWorker : claude-main
 - SubWorker : codex-critic
@@ -274,56 +256,100 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>REQ-MiddleProxy-FUNC-01</t>
+    <t xml:space="preserve">REQ-FRONTEND-FUNC-01</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>MiddleProxy</t>
+    <t xml:space="preserve">FRONTEND</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>MiddleProxy API 분석</t>
+    <t xml:space="preserve">FrontEnd API 분석</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>[개요]
-middle-proxy 의 엔드포인트 목록을 찾아내서, 각각 의 호출되는 메소드들을 분석한다.
+    <t xml:space="preserve">[개요]
+FrontEnd 의 엔드포인트 Rest API 목록을 찾아낸다.
 [상세 기능 요구사항]
-1. 엔드포인트를 전수 식별해 1건 = 1행인 표로 만든다.
-   열 = HTTP · 경로 · 컨트롤러 · 컨트롤러 메서드 · 파일:라인 · 호출 메서드 · Feign
-2. 상속으로 생기는 엔드포인트는 부모를 1회만 기재하고 상속 컨트롤러 목록을 붙인다.
-3. 호출 메서드가 Feign 이면 어느 클라이언트의 어느 메서드인지 적는다.
-   서비스를 거쳐 나가면 그 표시를 남긴다.
-4. 추출하지 못한 행은 비우지 말고 사유를 적는다.
-5. 호출 메서드가 다시 무엇을 부르는지 체인으로 전개한다. 최대 깊이를 명시한다.
-   같은 클래스의 로컬 메서드를 거친 경우 그 경로를 표시한다.
+각 파일의 endpoint 를 찾아낸다.
+함수로 조합해서 파싱하는 api들도 완성해서 나타내준다.
+js에 해당하는 메뉴들을 찾아야한다.
+ex) menuname,jsfilename,apiuril,etc…
 [입력 / 출력]
-- 출력 : 엔드포인트 카탈로그 1건 (PDF)
-         표 원본 CSV 1건 (검색·필터용)
+- 출력 : CSV
 [제약 조건 / 비기능 요구사항]
 - 읽기 전용. 코드 수정·실행 금지.
 - 레퍼런스 문서다. 구조 비평·결함 지적·개선 권고는 이 요구사항의 산출물이 아니다.
 - 설명 문단을 늘리지 않는다. 표로 표현할 수 있으면 표로 한다.
 [검증 기준]
-- 자체 선언 엔드포인트가 표에 빠짐없이 있다.
-- 상속 엔드포인트가 1회 기재되고 상속 컨트롤러가 열거돼 있다.
-- Feign 클라이언트가 전수 기재돼 있다.
-- 호출 메서드가 비어 있는 행은 전부 사유가 적혀 있다.
-- 호출 체인이 전개돼 있고, 깊이 상한과 잘린 경로의 처리 방식이 적혀 있다.
+- / 로 끝나는 api는 존재 하면 안된다.
 [작업 대상]
-Java-Service-Tree-Framework-Middle-Proxy
-게이트웨이 경로 규칙 — 프론트가 부르는 외부 경로는 내부 경로와 다르다.
-  /{권한}/{서비스}/**  →  rewrite  →  내부 경로
-  권한   auth-anon → /anonymous/    auth-user → /
-         auth-manager → /manager/   auth-admin → /admin/
-  서비스 api=Backend-Core  ai=AI  yml=Global-Config
-         search=Engine-Fire  hub=Broker-Hub
-  예외   /dwr/** 는 Backend-Core 로 변환 없이 전달. *-api/** 는 스웨거.
-         auth-anon 계열은 쿠키를 떼고(RemoveRequestHeader=Cookie) 넘긴다.
+Java-Service-Tree-Framework-Frontend-Web/arms/js/,
+Java-Service-Tree-Framework-Frontend-Web/backoffice/js/
 [Worker Settings]
 - MainWorker : claude-main
 - SubWorker : codex-critic
-- MainWorker-SubAgent : backend-expert,frontend-expert</t>
+- MainWorker-SubAgent : frontend-expert</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">REQ-MAPPING-FUNC-01</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">MAPPING</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">FrontEnd-Backend API 매핑 분석</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">[개요]
+FrontEnd 의 엔드포인트 와  Backend의 엔드포인트가 부합되는것끼리 매핑한다. 서로 사용하지 않는 값을 찾아내기 위함이다
+[상세 기능 요구사항]
+FrontEnd 와 Backend 의 서로의 엔드포인트가 매핑 되는부분을 찾아서 매핑이 되었는지 안되었는지 체크를 해야한다.
+menu 별로 나타내면 되며 매핑이 안되는 것만 체크한다. 
+ex) backendurl,frontendurl, no mapping
+1. 경로 대조는 게이트웨이 rewrite 규칙을 적용한 뒤에 한다.
+   /{권한}/{서비스}/** → 내부 경로. auth-anon→/anonymous, auth-user→(없음), auth-manager→/manager, auth-admin→/admin
+   서비스 세그먼트가 api 인 것만 Backend-Core 대상. ai·yml·search·hub 는 대상 외로 분류한다.
+   api 여도 Middle-Proxy 가 직접 처리하는 구간(/auth-user/api/aichat/**,
+   /auth-user/api/arms/reqAdd/(sync|async)/**)이 있으므로 note 에 그 사실을 남긴다.
+2. 상속으로 생긴 URL 은 provider 컬럼에 상속(&lt;부모클래스&gt;) 로 표기한다.
+   TreeAbstractController · TreeMapAbstractController 상속분은 프레임워크 공통 트리 CRUD 라
+   프론트가 호출하지 않는 것이 정상이다. 목록에서 빼지 말고 표기해 구분만 한다.
+   프론트가 Tree CRUD 액션을 부르는 호출도 같은 기준으로 상속 표기한다.
+   상속 액션 목록은 손으로 적지 말고 백엔드 카탈로그의 상속 행에서 읽는다.
+3. 메뉴명은 추정하지 않는다. js 는 html 폴더와 1:1 이므로 그 구조로 확정한다.
+   순서 = 네비게이션(page-navigation.html · page-sidebar.html) 라벨
+        → html/&lt;page&gt;/content-header.html 의 breadcrumb·h3
+        → 공통 모듈 → 페이지 키. 어느 것으로 정했는지 menusource 컬럼에 남긴다.
+   한 이름이 여러 페이지를 덮으면 이름 (page) 로 구분한다.
+4. 백엔드 쪽 미호출 행의 메뉴명은 같은 basePath 를 실제 호출하는 프론트 메뉴를
+   건수 순으로 전부 적는다. 호출이 없으면 (호출 메뉴 없음) &lt;basePath&gt; 로 둔다.
+[입력 / 출력]
+- 입력 : backend-core_endpoints_flat.csv,frontend-web_api-calls_flat.csv
+- 출력 : CSV
+         엑셀은 한 시트에 menuname 기준 정렬로 낸다 (시트 분할하지 않는다)
+[제약 조건 / 비기능 요구사항]
+- 읽기 전용. 코드 수정·실행 금지.
+- 레퍼런스 문서다. 구조 비평·결함 지적·개선 권고는 이 요구사항의 산출물이 아니다.
+- 설명 문단을 늘리지 않는다. 표로 표현할 수 있으면 표로 한다.
+[검증 기준]
+- url을 추론해서 검증하며, 애매한경우에는 note에 남긴다
+- 매핑이 성립한 행은 산출물에 싣지 않는다 (미매핑만).
+- menuname 에 추정 표현이 0건이어야 한다.
+- 상속으로 생긴 URL 이 provider 로 구분돼 있어야 한다.
+[작업 대상]
+Java-Service-Tree-Framework-Frontend-Web/arms/js/,
+Java-Service-Tree-Framework-Frontend-Web/backoffice/js/
+Java-Service-Tree-Framework-Backend-Core
+(경로 판정 참조용으로 Java-Service-Tree-Framework-Middle-Proxy 읽기)
+[Worker Settings]
+- MainWorker : claude-main
+- SubWorker : codex-critic
+- MainWorker-SubAgent : frontend-expert</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
@@ -1004,18 +1030,38 @@
       </c>
       <c r="L3" s="3"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
+    <row r="4" spans="1:12" ht="226.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>56</v>
+      </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="2"/>
+      <c r="E4" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="L4" s="3"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.4">
